--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:42</t>
+    <t xml:space="preserve">2026-09-24 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22">
@@ -1021,7 +1021,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.39</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>30</v>
@@ -1030,10 +1030,10 @@
         <v>-0.09</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:31</t>
+    <t xml:space="preserve">2026-10-01 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_residentes_a_2022_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:18</t>
+    <t xml:space="preserve">2026-10-05 19:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
